--- a/reports/history/build-9/Excel/Failed_Test_Cases.xlsx
+++ b/reports/history/build-9/Excel/Failed_Test_Cases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,46 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0058a6ff"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008b949e"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00cba6f7"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00ffffff"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001e2030"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00d63031"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +72,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="0030363d"/>
+      </left>
+      <right style="thin">
+        <color rgb="0030363d"/>
+      </right>
+      <top style="thin">
+        <color rgb="0030363d"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0030363d"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,468 +471,619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Failed Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated: 2026-06-23 13:02:07 | Total: 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Execution Time</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TC_AUTH_029</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TC_AUTHEN_019</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Verify Authentication Scenario 29</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC_AUTH_062</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Verify Authentication — Scenario 19</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>5.44s</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>TC_AUTHEN_028</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Verify Authentication — Scenario 28</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2.72s</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TC_AUTHOR_048</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Authorization</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Verify Authorization Scenario 22</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC_REGI_076</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Registration</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Verify Registration Scenario 6</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC_PROF_098</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Verify Profile Scenario 8</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TC_NAVI_112</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Verify Authorization — Scenario 8</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>3.40s</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TC_NAVIGA_109</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Verify Navigation Scenario 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TC_NAVI_127</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Verify Navigation Scenario 17</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TC_FORM_185</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Verify Forms Scenario 25</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Verify Navigation — Scenario 29</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>6.06s</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC_FORM_193</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Verify Forms Scenario 33</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_UI_VAL_117</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Verify UI Validation — Scenario 7</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>3.00s</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TC_CRUD_208</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Verify CRUD Scenario 8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_UI_VAL_151</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Verify UI Validation — Scenario 41</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>3.20s</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TC_SEAR_253</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Verify Search Scenario 13</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TC_UI_VAL_156</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Verify UI Validation — Scenario 46</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>0.82s</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TC_INPU_281</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>InputValidation</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Verify InputValidation Scenario 1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TC_CRUD_O_217</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Verify CRUD Operations — Scenario 7</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>5.91s</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TC_INPU_298</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>InputValidation</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Verify InputValidation Scenario 18</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TC_CRUD_O_225</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Verify CRUD Operations — Scenario 15</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>4.73s</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TC_SESS_356</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SessionMgmt</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Verify SessionMgmt Scenario 16</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TC_SESSIO_337</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Session Mgmt</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Verify Session Mgmt — Scenario 17</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>4.69s</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TC_FILE_387</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FileUpload</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Verify FileUpload Scenario 7</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TC_ACCESS_375</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Verify Accessibility — Scenario 15</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>4.42s</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TC_FILE_396</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FileUpload</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Verify FileUpload Scenario 16</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TC_PERFOR_413</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Performance Smoke</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Verify Performance Smoke — Scenario 13</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>2.26s</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TC_FILE_399</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FileUpload</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Verify FileUpload Scenario 19</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TC_ACCE_429</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Verify Accessibility Scenario 19</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TC_PERF_445</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PerformanceSmoke</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Verify PerformanceSmoke Scenario 5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TC_PERF_453</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PerformanceSmoke</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Verify PerformanceSmoke Scenario 13</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TC_REGR_464</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>TC_REGRES_432</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Regression</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Verify Regression Scenario 4</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Assertion failed - element not found</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Verify Regression — Scenario 12</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>5.82s</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23 13:02:06</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Element not found / assertion failed</t>
         </is>
       </c>
     </row>
